--- a/words_CZ/B1.9.xlsx
+++ b/words_CZ/B1.9.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PY_progs\Learn_CZ\words_CZ\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E0441C-65F5-4365-A40B-C0A4C0BF153B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,561 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="178">
+  <si>
+    <t>(M) břeh</t>
+  </si>
+  <si>
+    <t>берег</t>
+  </si>
+  <si>
+    <t>bank (river), shore</t>
+  </si>
+  <si>
+    <t>(M) chodník</t>
+  </si>
+  <si>
+    <t>тротуар</t>
+  </si>
+  <si>
+    <t>sidewalk, pavement</t>
+  </si>
+  <si>
+    <t>(Ž) dálnice</t>
+  </si>
+  <si>
+    <t>автострада, шосе</t>
+  </si>
+  <si>
+    <t>шоссе, автомагистраль</t>
+  </si>
+  <si>
+    <t>highway, motorway</t>
+  </si>
+  <si>
+    <t>(S) dědictví</t>
+  </si>
+  <si>
+    <t>спадщина</t>
+  </si>
+  <si>
+    <t>наследство</t>
+  </si>
+  <si>
+    <t>heritage, inheritance</t>
+  </si>
+  <si>
+    <t>(Ž-Pl) dopravní značky</t>
+  </si>
+  <si>
+    <t>дорожні знаки</t>
+  </si>
+  <si>
+    <t>дорожные знаки</t>
+  </si>
+  <si>
+    <t>traffic signs</t>
+  </si>
+  <si>
+    <t>(Ž) hlavní silnice</t>
+  </si>
+  <si>
+    <t>головна дорога</t>
+  </si>
+  <si>
+    <t>главная дорога</t>
+  </si>
+  <si>
+    <t>main road</t>
+  </si>
+  <si>
+    <t>jedinečný</t>
+  </si>
+  <si>
+    <t>унікальний</t>
+  </si>
+  <si>
+    <t>уникальный</t>
+  </si>
+  <si>
+    <t>unique</t>
+  </si>
+  <si>
+    <t>jet tramvají / autobusem</t>
+  </si>
+  <si>
+    <t>їхати трамваєм / автобусом</t>
+  </si>
+  <si>
+    <t>ехать на трамвае / автобусе</t>
+  </si>
+  <si>
+    <t>to go by tram / bus</t>
+  </si>
+  <si>
+    <t>(M) kopec</t>
+  </si>
+  <si>
+    <t>пагорб, гора</t>
+  </si>
+  <si>
+    <t>холм, горка</t>
+  </si>
+  <si>
+    <t>hill</t>
+  </si>
+  <si>
+    <t>(Ž) křižovatka</t>
+  </si>
+  <si>
+    <t>перехрестя</t>
+  </si>
+  <si>
+    <t>перекрёсток</t>
+  </si>
+  <si>
+    <t>intersection, crossroads</t>
+  </si>
+  <si>
+    <t>lákat</t>
+  </si>
+  <si>
+    <t>вабити, приваблювати</t>
+  </si>
+  <si>
+    <t>манить, привлекать</t>
+  </si>
+  <si>
+    <t>to lure, to attract</t>
+  </si>
+  <si>
+    <t>(Ž) lanovka</t>
+  </si>
+  <si>
+    <t>канатна дорога, фунікулер</t>
+  </si>
+  <si>
+    <t>канатная дорога</t>
+  </si>
+  <si>
+    <t>cable car, funicular</t>
+  </si>
+  <si>
+    <t>mít zpoždění</t>
+  </si>
+  <si>
+    <t>запізнюватися (про транспорт)</t>
+  </si>
+  <si>
+    <t>опаздывать (иметь опоздание)</t>
+  </si>
+  <si>
+    <t>to be delayed</t>
+  </si>
+  <si>
+    <t>nastoupit do tramvaje</t>
+  </si>
+  <si>
+    <t>сісти в трамвай</t>
+  </si>
+  <si>
+    <t>сесть в трамвай</t>
+  </si>
+  <si>
+    <t>to get on the tram</t>
+  </si>
+  <si>
+    <t>Nejsem odtud (odsud).</t>
+  </si>
+  <si>
+    <t>Я не місцевий / Я не звідси.</t>
+  </si>
+  <si>
+    <t>Я не отсюда.</t>
+  </si>
+  <si>
+    <t>I am not from here.</t>
+  </si>
+  <si>
+    <t>(Ž) noční linka</t>
+  </si>
+  <si>
+    <t>нічний маршрут</t>
+  </si>
+  <si>
+    <t>ночной маршрут</t>
+  </si>
+  <si>
+    <t>night line/route</t>
+  </si>
+  <si>
+    <t>(Ž) památka</t>
+  </si>
+  <si>
+    <t>пам'ятка (історична)</t>
+  </si>
+  <si>
+    <t>достопримечательность</t>
+  </si>
+  <si>
+    <t>monument, landmark</t>
+  </si>
+  <si>
+    <t>(Ž) pěší zóna</t>
+  </si>
+  <si>
+    <t>пішохідна зона</t>
+  </si>
+  <si>
+    <t>пешеходная зона</t>
+  </si>
+  <si>
+    <t>pedestrian zone</t>
+  </si>
+  <si>
+    <t>(M) plakát</t>
+  </si>
+  <si>
+    <t>плакат, афіша</t>
+  </si>
+  <si>
+    <t>плакат</t>
+  </si>
+  <si>
+    <t>poster</t>
+  </si>
+  <si>
+    <t>(M) počátek / začátek</t>
+  </si>
+  <si>
+    <t>початок</t>
+  </si>
+  <si>
+    <t>начало</t>
+  </si>
+  <si>
+    <t>beginning, start</t>
+  </si>
+  <si>
+    <t>(M) podchod</t>
+  </si>
+  <si>
+    <t>підземний перехід</t>
+  </si>
+  <si>
+    <t>подземный переход</t>
+  </si>
+  <si>
+    <t>underpass, subway</t>
+  </si>
+  <si>
+    <t>pokračovat</t>
+  </si>
+  <si>
+    <t>продовжувати</t>
+  </si>
+  <si>
+    <t>продолжать</t>
+  </si>
+  <si>
+    <t>to continue</t>
+  </si>
+  <si>
+    <t>(M) poloviční úvazek</t>
+  </si>
+  <si>
+    <t>півставки (неповна зайнятість)</t>
+  </si>
+  <si>
+    <t>полставки</t>
+  </si>
+  <si>
+    <t>part-time job</t>
+  </si>
+  <si>
+    <t>(Ž) pověst</t>
+  </si>
+  <si>
+    <t>легенда, переказ</t>
+  </si>
+  <si>
+    <t>легенда, сказание</t>
+  </si>
+  <si>
+    <t>legend, myth</t>
+  </si>
+  <si>
+    <t>(M) požár</t>
+  </si>
+  <si>
+    <t>пожежа</t>
+  </si>
+  <si>
+    <t>пожар</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>(M) přechod pro chodce</t>
+  </si>
+  <si>
+    <t>пішохідний перехід</t>
+  </si>
+  <si>
+    <t>пешеходный переход</t>
+  </si>
+  <si>
+    <t>pedestrian crossing</t>
+  </si>
+  <si>
+    <t>přestoupit na tramvaj</t>
+  </si>
+  <si>
+    <t>пересісти на трамвай</t>
+  </si>
+  <si>
+    <t>пересесть на трамвай</t>
+  </si>
+  <si>
+    <t>to transfer to the tram</t>
+  </si>
+  <si>
+    <t>(M) průchod</t>
+  </si>
+  <si>
+    <t>прохід, арка</t>
+  </si>
+  <si>
+    <t>проход</t>
+  </si>
+  <si>
+    <t>passage, passageway</t>
+  </si>
+  <si>
+    <t>rovně</t>
+  </si>
+  <si>
+    <t>прямо</t>
+  </si>
+  <si>
+    <t>прямо (ровно)</t>
+  </si>
+  <si>
+    <t>straight, straight ahead</t>
+  </si>
+  <si>
+    <t>(Ž) sbírka</t>
+  </si>
+  <si>
+    <t>колекція, збірка</t>
+  </si>
+  <si>
+    <t>коллекция, сбор</t>
+  </si>
+  <si>
+    <t>collection</t>
+  </si>
+  <si>
+    <t>(M) semafor</t>
+  </si>
+  <si>
+    <t>світлофор</t>
+  </si>
+  <si>
+    <t>светофор</t>
+  </si>
+  <si>
+    <t>traffic light</t>
+  </si>
+  <si>
+    <t>shořet</t>
+  </si>
+  <si>
+    <t>згоріти</t>
+  </si>
+  <si>
+    <t>сгореть</t>
+  </si>
+  <si>
+    <t>to burn down</t>
+  </si>
+  <si>
+    <t>(Ž) síň</t>
+  </si>
+  <si>
+    <t>зала</t>
+  </si>
+  <si>
+    <t>зал</t>
+  </si>
+  <si>
+    <t>hall</t>
+  </si>
+  <si>
+    <t>(Ž) slepá ulice</t>
+  </si>
+  <si>
+    <t>тупик (глухий кут)</t>
+  </si>
+  <si>
+    <t>тупик</t>
+  </si>
+  <si>
+    <t>dead end, cul-de-sac</t>
+  </si>
+  <si>
+    <t>(M) sloup</t>
+  </si>
+  <si>
+    <t>стовп, колона</t>
+  </si>
+  <si>
+    <t>столб</t>
+  </si>
+  <si>
+    <t>column, pole</t>
+  </si>
+  <si>
+    <t>(Ž) stanice metra</t>
+  </si>
+  <si>
+    <t>станція метро</t>
+  </si>
+  <si>
+    <t>станция метро</t>
+  </si>
+  <si>
+    <t>metro station</t>
+  </si>
+  <si>
+    <t>(M) trh / (S) tržiště</t>
+  </si>
+  <si>
+    <t>ринок / базар</t>
+  </si>
+  <si>
+    <t>рынок</t>
+  </si>
+  <si>
+    <t>market / marketplace</t>
+  </si>
+  <si>
+    <t>venku</t>
+  </si>
+  <si>
+    <t>надворі, на вулиці</t>
+  </si>
+  <si>
+    <t>на улице, снаружи</t>
+  </si>
+  <si>
+    <t>outside, outdoors</t>
+  </si>
+  <si>
+    <t>vrátit se zpátky</t>
+  </si>
+  <si>
+    <t>повернутися назад</t>
+  </si>
+  <si>
+    <t>вернуться обратно</t>
+  </si>
+  <si>
+    <t>to return, to come back</t>
+  </si>
+  <si>
+    <t>vydržet</t>
+  </si>
+  <si>
+    <t>витримати</t>
+  </si>
+  <si>
+    <t>выдержать, устоять</t>
+  </si>
+  <si>
+    <t>to endure, to last</t>
+  </si>
+  <si>
+    <t>(Ž) výluka</t>
+  </si>
+  <si>
+    <t>припинення руху (ремонт)</t>
+  </si>
+  <si>
+    <t>перерыв в движении (закрытие)</t>
+  </si>
+  <si>
+    <t>service suspension</t>
+  </si>
+  <si>
+    <t>(Ž) výzdoba</t>
+  </si>
+  <si>
+    <t>оздоблення, прикраса</t>
+  </si>
+  <si>
+    <t>украшение, декор</t>
+  </si>
+  <si>
+    <t>decoration</t>
+  </si>
+  <si>
+    <t>zahnout (odbočit)</t>
+  </si>
+  <si>
+    <t>повернути (звернути)</t>
+  </si>
+  <si>
+    <t>повернуть (свернуть)</t>
+  </si>
+  <si>
+    <t>to turn</t>
+  </si>
+  <si>
+    <t>zapáchat</t>
+  </si>
+  <si>
+    <t>смердіти, мати запах</t>
+  </si>
+  <si>
+    <t>вонять, пахнуть</t>
+  </si>
+  <si>
+    <t>to stink, to smell bad</t>
+  </si>
+  <si>
+    <t>(Ž) zastávka</t>
+  </si>
+  <si>
+    <t>зупинка</t>
+  </si>
+  <si>
+    <t>остановка</t>
+  </si>
+  <si>
+    <t>stop (bus/tram)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +589,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +597,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +903,641 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>